--- a/www/download/COUNTRY.WAS.EXI382.xlsx
+++ b/www/download/COUNTRY.WAS.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resto do mundo - Asia</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1195</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>768.486</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>304.7</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>311.522</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>320.948</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>366.697</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>367.642</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>375.327</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>392.807</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>416.161</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>444.073</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>461.459</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>466.145</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>467.728</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>495.106</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>497.754</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>533.626</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>532.475</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>528.534</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>528.691</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>522.242</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>512.582</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>561.923</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>555.926</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>574.311</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>564.709</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>603.868</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>627.844</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>410.522</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>67.591</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>120.137</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>123.042</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>145.331</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>145.489</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>147.584</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>155.386</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>166.374</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>183.359</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>192.643</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>200.094</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>203.956</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>224.072</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>228.691</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>238.196</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>246.135</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>231.226</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>221.405</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>219.192</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>218.871</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>243.879</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>244.634</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>257.521</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>261.808</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>289.832</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>310.542</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1551016.073</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>577496</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>588306</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>604175</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>698030</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>700208</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>716599</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>762391</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>809364</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>871179</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>918656</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>945169</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>948168</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1045459</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1044864</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1079549</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1115461</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1076200</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1054950</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1037512.807</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1024370.485</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1123437.035</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>1111130.743</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1146094.996</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1136763.101</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>1222315.802</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1269912.792</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>878615.746</t>
+          <t>2354761014128.62</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-83866</t>
+          <t>838761886992.354</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-97800</t>
+          <t>890920086319.177</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-102469</t>
+          <t>929497982196.844</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-100492</t>
+          <t>1031792046175.92</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-101676</t>
+          <t>1072246293726.69</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-108887</t>
+          <t>1089344472943.15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-113995</t>
+          <t>1143189575653.93</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-114512</t>
+          <t>1192937719717.06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-100559</t>
+          <t>1255609442968.71</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-98112</t>
+          <t>1301553439064.64</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-82373</t>
+          <t>1327724849986.55</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-69760</t>
+          <t>1356731411765.55</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-52725</t>
+          <t>1449372926636.6</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-40880</t>
+          <t>1448186807354.41</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-58985</t>
+          <t>1495601378766.61</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-22299</t>
+          <t>1498785359719.06</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-63600</t>
+          <t>1544295032290.17</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-96050</t>
+          <t>1523412265468.18</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>473758.836</t>
+          <t>1621574962307.54</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>480490.444</t>
+          <t>1615190075271.75</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>533886.511</t>
+          <t>1719904919862.57</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>533988.354</t>
+          <t>1699927172733.66</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>558401.285</t>
+          <t>1733344687316.83</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>570689.117</t>
+          <t>1689163329642.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>633523.882</t>
+          <t>1825069465941.82</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>675878.117</t>
+          <t>1932510433326.3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>422849759348.402</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>203544330227.882</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>204328487852.153</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>240107243547.79</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>244022421602.903</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>242859934172.392</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>219585641302.526</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>245828453908.293</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>307704026171.059</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>243134843825.721</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>249570398148.84</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>257341433494.4</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>320431882736.033</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>291125074496.287</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>310578849516.615</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>298307146898.667</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>268633371953.814</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>290768484555.806</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>280967332574.466</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>308234683958.007</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>277575940870.693</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>307262534267.292</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>329092167176.308</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>311916348756.94</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>335483647160.722</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>356528195434.201</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>355455076658.732</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2652177000377.21</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>93373883.5932273</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>88523942.1313307</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>99895951.0818809</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>114404977.949716</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>95209289.0557627</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>97603304.2884161</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>102707826.879962</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>115785463.047151</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>105126702.189768</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>99720733.2683493</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>95026711.8347853</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>86176164.469446</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>92723127.6775709</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>84672724.0485234</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>67155512.5613336</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>63363263.2718377</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>55988707.3298112</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>55720377.6133612</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>624700925828.909</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>484777665320.777</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>544088890605.127</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>516181254234.533</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>526533679520.195</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>458115339511.216</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>481892862870.33</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>465294582237.605</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4551368.26720597</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3453692.75738053</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3976577.72548952</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4318219.06735673</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5160932.80580631</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6270577.80107795</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6345255.0107193</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6535708.32018757</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6331348.01563615</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6635836.11287968</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>7441603.86360285</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7909010.80717277</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>8312666.97167346</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>9050609.53977096</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>9078149.83551416</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>10956515.9974369</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>11486069.180023</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>12738094.0383485</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>12613194.9251526</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>12910463.2185897</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>14201113.6125468</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>13910624.4513409</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>14581078.031184</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14485619.0422367</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>15262473.4786094</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15592313.4252421</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>15906251.6438126</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8777613.37645301</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6373812.33046589</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7373810.58530549</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7909043.50954074</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9260637.83469958</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>11503930.4787587</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>11735237.2853562</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11937913.4288277</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>11443590.9495006</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>11770612.5199926</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>13080315.017641</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>14273453.6011442</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>15111155.2744513</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>16220670.9190586</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>16241630.9722431</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>19343150.6532079</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>20180111.8596866</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>22950307.6124153</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>22115344.2452168</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>24366172.6772922</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>27416473.9949591</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26609401.9387145</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>27805862.8609915</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>27574835.4309073</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>28631100.0900447</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>29428254.1607994</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>30592915.9279166</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.07784378974365</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-1.4120281803311</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-1.47864104035731</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-1.42676346821399</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-1.41181461662437</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.41866107040986</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.49587486391973</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-1.46371767868151</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-1.37214982665296</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-1.41359353689349</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-1.39312354641219</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-1.32009225596455</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1.21770617643931</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-1.1811077252324</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-1.13162518974842</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-1.19773243991212</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-1.08300904626031</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-1.21873072006609</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-1.3418546886576</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.53700689989347</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.731023381362847</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.737558117402425</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.622610341424178</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.790227692432811</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.701093694889782</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.776925051930084</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.901444547313041</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1030.03013364493</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3011.41457924435</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1700.79565706018</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1951.425070688</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1679.08031736504</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1669.2666399007</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1487.86888349861</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1582.05020985237</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1849.47182956015</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1326.00441661325</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1295.50722397856</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1286.10269920353</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1571.08338433838</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1299.24789574908</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1358.07202520657</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1252.36001821352</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1091.40663438247</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1257.5077394226</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1269.01981696144</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1406.23327259039</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1268.21468350401</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1259.89541694586</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1345.24062604794</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1211.22652401492</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1281.41189148365</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1230.11989514254</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1144.62633312732</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>-586041221839.184</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>-152294319855.895</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>-157580012560.766</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>-166599842035.441</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>-230867195009.772</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>-254124950339.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-311861585039.025</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>-330490879458.205</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-271039507909.997</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>-396151098754.049</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>-406939637439.211</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>-410531596619.917</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>-267313964351.869</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>-429901994990.201</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-399123842764.326</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>-428640492791.775</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>-469645845050.638</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>-472312531628.727</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>-501114526991.52</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>-451803004314.318</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>-461769650624.522</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>-488459425826.377</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>-448726572489.087</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>-501739854503.069</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>-459967904203.942</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>-525965255401.621</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>-565633204647.562</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-659068748088.493</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-188737200101.88</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-195179950859.365</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-201966490425.671</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-267810822153.826</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-295010873608.203</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-335513320482.529</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-354895796008.772</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-301363153816.677</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-420446725260.298</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-431808003850.327</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-431197557250.472</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-286635571821.887</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-447578594068.573</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-421391634163.227</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-454677972308.453</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-488086555261.039</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-493508325297.971</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-528538528184.902</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-472627111068.817</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-484100664054.928</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-512082768738.516</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-469012973448.714</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-524635005840.607</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-478722826875.924</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-547522139681.506</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-588856202915.231</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>73027526249.3099</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>36442880245.985</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>37599938298.5991</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>35366648390.2297</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>36943627144.0543</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>40885923268.8532</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23651735443.5042</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>24404916550.5663</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>30323645906.6807</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>24295626506.2495</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>24868366411.1166</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>20665960630.5555</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>19321607470.0176</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>17676599078.372</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>22267791398.9008</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>26037479516.6772</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>18440710210.4013</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>21195793669.2442</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>27424001193.382</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>20824106754.4987</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>22331013430.4063</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>23623342912.1387</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>20286400959.6274</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>22895151337.5383</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>18754922671.9819</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>21556884279.8849</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>23222998267.6686</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>2140.24171644293</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>-1240.7876693086</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>-814.070602730473</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>-832.796931126534</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>-691.46981717721</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>-698.8569582603</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.004</t>
+          <t>-737.796780135277</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-733.624650870339</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>-688.280620770336</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>-548.426856603455</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>-509.294394293068</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>-411.671514390151</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.613</t>
+          <t>-342.034556471633</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>-235.303830912098</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.788</t>
+          <t>-178.756488009843</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.596</t>
+          <t>-247.63220204975</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4.008</t>
+          <t>-90.596623802269</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>-275.055573332581</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.686</t>
+          <t>-433.820374427683</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>4.964</t>
+          <t>2161.39024283121</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>5.627</t>
+          <t>2195.30926973312</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>5.759</t>
+          <t>2189.1415087924</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>6.016</t>
+          <t>2182.80135152932</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5.995</t>
+          <t>2168.37126510065</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>6.684</t>
+          <t>2179.80168915962</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>6.877</t>
+          <t>2185.83085855639</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>7.304</t>
+          <t>2176.44349983587</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>2018.27601219152</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>1895.29373153868</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>1888.48941647875</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>1882.47005745445</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>1903.56070543213</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>1904.59196718569</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1909.26578690007</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>1940.87936314741</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1944.83385036095</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>1961.79231792969</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>1990.76407654845</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>2027.62874212912</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>2027.17818903316</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>2111.58620578259</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>2099.15741510872</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>2023.04422947893</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>2094.86079158593</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>2036.19823890233</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1995.39995952242</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1986.64971521854</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1998.45225671683</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>1999.2721439376</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>1998.70218974752</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1995.60033799987</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>2013.00686747735</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>2024.14365564814</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>2022.6559842685</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>504250.420072543</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>564237.468254823</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>636891.148606078</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>583930.198964474</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>657301.315934692</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>867061.057239494</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>785629.888077579</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>784557.849233116</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>667076.625394982</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>785789.471434709</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>899882.770097536</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1021355.30639589</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>779993.60404998</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1040257.37803203</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>989247.584546747</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1378228.34031063</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1593077.66743938</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1862718.5350873</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1893831.05181567</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1881790.55948875</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2060665.99937705</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2042745.5855965</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2195051.43297788</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2315919.14013585</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2443459.74961361</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2602337.77894536</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2825494.58854433</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>764463829340.333</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>246477709502.908</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>270525015470.929</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>275501923029.687</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>332584680162.269</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>361848735948.21</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>418738472526.076</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>442132214055.083</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>372727998405.425</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>518978740389.576</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>534729045199.7</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>539007952578.036</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>356366520136.812</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>551119092517.62</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>514007500770.624</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>555211630736.526</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>608689023768.37</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>624008667874.592</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>664416404295.438</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>617591823804.528</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>625907364521.045</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>675032961250.228</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>644083505041.23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>705815300317.208</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>657139242244.725</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>743298395771.276</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>797746692726.627</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>599457.346110505</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>654303.841455942</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>745535.000246715</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>601812.038129208</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>646221.073626202</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>833259.277145639</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>724885.749469269</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>771049.793404355</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>642086.368396649</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>789944.315000992</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>920339.78334601</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1073740.96697739</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>833478.640074036</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1104037.06032303</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1030288.07156318</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1489149.7985688</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1706982.93686672</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2065448.73374929</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2107361.59400407</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2020328.07456603</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2082876.23831906</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2190534.79643167</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2335045.0532477</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2548176.13669855</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2666469.31437875</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2820477.49823997</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3006453.6438797</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1551016.073</t>
+          <t>232359829302.679</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>577496</t>
+          <t>112479296963.104</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>588306</t>
+          <t>133281797485.136</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>604175</t>
+          <t>112270989460.807</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>698030</t>
+          <t>99684882369.6372</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>700208</t>
+          <t>102479757894.793</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>716599</t>
+          <t>97080134251.4678</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>762391</t>
+          <t>109380983651.348</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>809364</t>
+          <t>97443204186.3867</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>871179</t>
+          <t>123589597739.227</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>918656</t>
+          <t>131210855179.671</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>945169</t>
+          <t>136270907430.4</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>948168</t>
+          <t>95694456137.4018</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1045459</t>
+          <t>129957423696.523</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1044864</t>
+          <t>120924465156.691</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1079549</t>
+          <t>140247977408.32</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1115461</t>
+          <t>152178250895.19</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1076200</t>
+          <t>173800059477.335</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1054950</t>
+          <t>187762560398.754</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1037512.807</t>
+          <t>180516201388.493</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>1024370.485</t>
+          <t>166284664054.188</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1123437.035</t>
+          <t>202247546553.77</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1111130.743</t>
+          <t>208841504022.173</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>1146094.996</t>
+          <t>227159400454.926</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1136763.101</t>
+          <t>217524842551.845</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>1222315.802</t>
+          <t>238501708076.453</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1269912.792</t>
+          <t>249745247024.089</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>878615.746</t>
+          <t>-95206.9260379615</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-83866</t>
+          <t>-90066.3732011192</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-97800</t>
+          <t>-108643.851640638</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-102469</t>
+          <t>-17881.8391647339</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-100492</t>
+          <t>11080.2423084904</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-101676</t>
+          <t>33801.7800938549</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-108887</t>
+          <t>60744.1386083097</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-113995</t>
+          <t>13508.0558287602</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-114512</t>
+          <t>24990.2569983331</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-100559</t>
+          <t>-4154.84356628334</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-98112</t>
+          <t>-20457.0132484737</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-82373</t>
+          <t>-52385.6605814957</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-69760</t>
+          <t>-53485.036024056</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-52725</t>
+          <t>-63779.6822909974</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-40880</t>
+          <t>-41040.4870164303</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-58985</t>
+          <t>-110921.458258174</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-22299</t>
+          <t>-113905.269427332</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-63600</t>
+          <t>-202730.198661993</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-96050</t>
+          <t>-213530.542188393</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>473758.836</t>
+          <t>-138537.515077282</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>480490.444</t>
+          <t>-22210.2389420079</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>533886.511</t>
+          <t>-147789.210835171</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>533988.354</t>
+          <t>-139993.620269825</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>558401.285</t>
+          <t>-232256.996562707</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>570689.117</t>
+          <t>-223009.564765137</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>633523.882</t>
+          <t>-218139.719294605</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>675878.117</t>
+          <t>-180959.055335365</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1848723.781</t>
+          <t>532104000037.654</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>667571.981</t>
+          <t>133998412539.804</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>707555.534</t>
+          <t>137243217985.793</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>739669.369</t>
+          <t>163230933568.88</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>820754.493</t>
+          <t>232899797792.632</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>848434.612</t>
+          <t>259368978053.417</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>863016.763</t>
+          <t>321658338274.608</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>907757.857</t>
+          <t>332751230403.735</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>944793.164</t>
+          <t>275284794219.038</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>998276.251</t>
+          <t>395389142650.349</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1037200.164</t>
+          <t>403518190020.029</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1057480.533</t>
+          <t>402737045147.637</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1079512.236</t>
+          <t>260672063999.41</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1156377.326</t>
+          <t>421161668821.097</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1153070.716</t>
+          <t>393083035613.933</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1195113.165</t>
+          <t>414963653328.206</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1200024.18</t>
+          <t>456510772873.18</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1231472.241</t>
+          <t>450208608397.257</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1216545.46</t>
+          <t>476653843896.684</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1283125.256</t>
+          <t>437075622416.035</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1269975.987</t>
+          <t>459622700466.857</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1358827.972</t>
+          <t>472785414696.457</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1344146.085</t>
+          <t>435242001019.057</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1369086.882</t>
+          <t>478655899862.282</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1340935.383</t>
+          <t>439614399692.879</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1448419.939</t>
+          <t>504796687694.823</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1525925.319</t>
+          <t>548001445702.538</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5.993</t>
+          <t>322373.16669837</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.326</t>
+          <t>381253.055616986</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>432246.40347639</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5.452</t>
+          <t>375533.275164713</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>421015.729847945</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>492008.28667327</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8.077</t>
+          <t>495953.864141292</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8.249</t>
+          <t>512893.140471503</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7.906</t>
+          <t>486243.849511496</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8.188</t>
+          <t>480495.840930133</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9.095</t>
+          <t>515892.681192954</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9.941</t>
+          <t>613941.198809916</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>10.473</t>
+          <t>679429.116069317</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>11.374</t>
+          <t>696101.608240888</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>732370.497791169</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>13.471</t>
+          <t>907825.782814797</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>14.098</t>
+          <t>998182.149556775</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>15.965</t>
+          <t>1154087.47259392</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>15.333</t>
+          <t>1172991.8827544</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>16.612</t>
+          <t>1242746.17894103</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>18.359</t>
+          <t>1436404.01711798</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>17.829</t>
+          <t>1461027.38190939</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>18.502</t>
+          <t>1535707.19867383</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18.315</t>
+          <t>1469428.07842233</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>18.975</t>
+          <t>1684730.46885593</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19.524</t>
+          <t>1700393.87641965</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>20.184</t>
+          <t>1801063.87164831</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1220990.729</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>454488.727</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>480458.906</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>507491.95</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>575015.406</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>584461.443</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>589009.69</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>625867.633</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>660011.695</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>707866.177</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>740474.911</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>735700.727</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>746339.786</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>808703.197</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>809454.226</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>847151.569</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>853075.169</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>857129.049</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>868858.094</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>859194.597</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>836631.938</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>899116.466</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>891422.463</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>910561.039</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>900447.78</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>966997.736</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1004775.005</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.958</t>
+          <t>442009.052479734</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.945</t>
+          <t>503143.382555743</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.409</t>
+          <t>553286.688403256</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.741</t>
+          <t>516247.941200953</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.477</t>
+          <t>549294.425003481</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5.442</t>
+          <t>663852.964919878</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.513</t>
+          <t>672145.301066017</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5.688</t>
+          <t>695528.847895902</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>5.523</t>
+          <t>626508.443024929</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>5.806</t>
+          <t>624957.276273511</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>6.493</t>
+          <t>700882.747845045</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6.916</t>
+          <t>807606.938475453</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>7.241</t>
+          <t>886389.451699192</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>7.954</t>
+          <t>922996.356290106</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>7.925</t>
+          <t>973836.14761402</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>9.549</t>
+          <t>1182858.71529125</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>1296772.23530917</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11.112</t>
+          <t>1521857.07589896</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>10.951</t>
+          <t>1566720.78027757</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>11.124</t>
+          <t>1654305.87625806</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>12.095</t>
+          <t>1815093.566414</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>11.797</t>
+          <t>2017183.60923772</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>2095502.26025806</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12.181</t>
+          <t>1998738.28382713</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>12.742</t>
+          <t>2263677.17848798</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13.034</t>
+          <t>2364903.06367775</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>13.291</t>
+          <t>2513826.40436361</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>411747.44</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>198832.178</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>201262.607</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>233472.92</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>234261.973</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>232986.647</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>209834.19</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>235872.1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>293216.409</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>235457.113</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>242277.53</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>247762.831</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>304831.5</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>278678.402</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>296335.449</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>286168.092</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>258962.504</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>279644.576</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>273512.914</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>296360.518</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>264950.729</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>295995.758</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>317429.309</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>300951.011</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>326419.096</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>346168.437</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>342814.078</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>113.39</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-142.18</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-148.59</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-143.89</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-142.9</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-143.64</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-151.89</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-148.33</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-139.05</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-142.71</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-140.5</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-133.25</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-122.88</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-118.92</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-113.8</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-120.61</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-108.61</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-122.74</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-135.12</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>59.86</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>81.35</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>80.37</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>68.22</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>85.55</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>74.83</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>83.01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>97.16</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2969065.076</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>94.798</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>101.075</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>116.606</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>96.31</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>98.986</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>104.451</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>116.126</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>106.443</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>101.359</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>96.497</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>87.776</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>94.846</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>86.211</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>68.559</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>65.191</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>57.334</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>57.044</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>699345.864</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>542702.041</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>609101.493</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>577858.789</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>589448.514</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>512854.611</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>539473.965</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>520891.494</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>184367.105753517</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>209362.852249482</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>237481.071518509</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>190682.273028724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>220316.952410823</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>251471.234077469</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>251786.36118118</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>252162.619205912</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>218052.560014716</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>251858.108935908</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>292136.508521063</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>326194.874181582</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>338991.953524026</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>390193.074164107</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>380565.822173092</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>459130.094644212</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>512414.844590844</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>600219.018312928</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>650029.195736893</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>646359.699511953</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>848182.101111133</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>767712.694012533</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>791300.112809569</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>883105.234306109</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>881606.173003235</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>956475.662935979</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>963256.908353107</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>878615746456.673</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-83866000000.5068</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-97800000000.1898</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-102468999999.755</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-100492000000.15</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-101676000000.282</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-108886999999.617</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-113995000000.219</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-114511999999.976</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-100558999999.925</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-98111999999.7757</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-82373000000.3728</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-69759999999.7098</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-52725000000.1353</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-40879999999.4719</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-58984999999.4972</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-22298999999.5785</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-63599999999.4159</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-96050000000.2014</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>473758836029.939</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>480490443750.961</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>533886510589.774</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>533988353741.971</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>558401285267.204</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>570689116923.732</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>633523882186.457</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>675878117327.484</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1551016072716.28</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>577495999999.906</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>588306000000.033</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>604174999999.944</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>698029999999.758</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>700208000000.028</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>716599000000.135</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>762390999999.802</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>809363999999.962</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>871179000000.029</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>918656000000.017</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>945168999999.879</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>948168000000.085</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1045459000000.1</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1044864000000.1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1079549000000.08</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1115461000000.06</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1076200000000.13</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1054949999999.89</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1037512807230.07</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1024370485374.47</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1123437034858.71</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1111130742771.35</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1146094995744.36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1136763100735.28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>1222315802204.1</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1269912791772.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1220990729132.52</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>454488727323.507</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>480458906485.63</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>507491949557.512</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>575015405518.453</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>584461442908.181</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>589009689984.474</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>625867633041.36</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>660011695440.561</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>707866176987.172</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>740474911175.022</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>735700726743.084</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>746339786150.129</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>808703197417.7</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>809454225960.818</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>847151569360.673</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>853075168633.191</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>857129049269.262</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>868858094301.398</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>859194596719.236</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>836631937754.266</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>899116465951.566</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>891422462840.827</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>910561039331.3</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>900447780163.038</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>966997735588.094</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1004775005076.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>768485610.167921</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>304700000.000037</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>311521999.999862</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>320948000.000028</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>366696999.999955</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>367641999.999972</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>375327000.000154</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>392806999.999977</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>416160999.999947</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>444073000.000019</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>461459000.000023</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>466145000.000049</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>467727999.999993</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>495105999.999956</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>497754000.000033</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>533626000.000076</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>532475000.000162</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>528534000.000061</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>528691000.00001</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>522242446.306617</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>512581915.295473</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>561923016.966606</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>555926114.69131</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>574310884.760153</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>564709002.786384</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>603868109.258634</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>627844181.931736</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>410521736.730245</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>67590936.044069</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>120136999.99995</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>123042000.000101</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>145330999.999955</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>145488999.999927</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>147584000.00018</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>155386000.000109</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>166373999.999902</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>183358999.999949</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>192642999.999953</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>200093999.999975</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>203955999.999946</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>224071999.999999</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>228691000.000072</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>238196000.000222</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>246135000.000078</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>231226000.00006</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>221405000.000093</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>219191715.888086</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>218871413.871164</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>243879396.761465</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>244634425.101417</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>257521068.580147</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>261807814.794267</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>289832069.899892</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>310542459.465846</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1551016072716.28</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>577495999999.906</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>588306000000.033</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>604174999999.944</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>698029999999.758</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>700208000000.028</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>716599000000.135</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>762390999999.802</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>809363999999.962</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>871179000000.029</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>918656000000.017</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>945168999999.879</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>948168000000.085</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1045459000000.1</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1044864000000.1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1079549000000.08</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1115461000000.06</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1076200000000.13</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1054949999999.89</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1037512807230.07</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>1024370485374.47</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1123437034858.71</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1111130742771.35</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>1146094995744.36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1136763100735.28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>1222315802204.1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1269912791772.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>878615746456.673</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-83866000000.5068</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-97800000000.1898</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-102468999999.755</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-100492000000.15</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-101676000000.282</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-108886999999.617</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-113995000000.219</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-114511999999.976</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-100558999999.925</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-98111999999.7757</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-82373000000.3728</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>-69759999999.7098</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>-52725000000.1353</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-40879999999.4719</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>-58984999999.4972</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-22298999999.5785</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>-63599999999.4159</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>-96050000000.2014</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>473758836029.939</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>480490443750.961</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>533886510589.774</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>533988353741.971</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>558401285267.204</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>570689116923.732</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>633523882186.457</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>675878117327.484</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1484455.69952338</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1622329.01919549</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1803970.60261967</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1642330.26155476</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1730834.81763596</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2209189.22032584</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2243494.0470982</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2193801.65194943</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1962943.11159275</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2096063.55581489</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2430878.31169162</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2739785.17894606</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2925374.54388834</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3043354.45788127</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>3120721.25122609</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>4025792.0579317</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4486979.31594339</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>5284150.10327034</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5245836.32417535</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>5556817.67024615</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>6299897.76900713</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>6447371.76440504</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>6735262.51919056</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>6711844.39168335</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>7482959.79087815</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>7698797.9716114</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>8176561.8559851</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>582459.652803746</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>655508.542549138</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>727508.773910537</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>660881.754495499</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>710974.412269718</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>859268.937660909</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>870594.804644848</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>883259.722784698</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>821593.429971069</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>823217.663937345</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>919073.029959849</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1054094.82542112</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1164745.52333473</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1186982.05790918</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1242815.90297359</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1551833.03243212</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1710505.30344963</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1994634.86902034</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2038115.74344088</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2158668.07099103</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2426261.43343581</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2565238.41231016</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2726908.34597114</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2671493.80102604</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2981007.74027622</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>3054532.59846986</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>3216295.43158215</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3609,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3673,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4034,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
